--- a/output/track2/lostanos_track2_methods_description.xlsx
+++ b/output/track2/lostanos_track2_methods_description.xlsx
@@ -709,6 +709,7 @@
 3) Drugs: each protein was resolved to UniProt and mapped to approved drugs via ChEMBL (all targets containing the protein, salts collapsed to parent), cross-checked with DGIdb, with STRING network distance to BUB1B as supporting evidence only. Each drug-target link records whether the drug acts in the desired direction.
 4) Prioritisation: surviving routes were scored 0-3 on mechanistic relevance (weight 0.35), directionality (0.20), experimental evidence (0.20), human exposure (0.15) and tractability (0.10), so drug availability alone cannot carry a hypothesis. Routes were discarded with an explicit category (no approved drug, wrong direction, phenotype not present in this child, published negative result, toxicity rather than rescue).
 5) Follow-up: for the two prioritised hypotheses we searched for ways to mitigate their tumour-related drawbacks (remission-maintenance framing for H1; senomorphic rapalogs as an alternative to senolytics for H2).
+6) Scalability: we re-ran the drug lookup automatically for all eight genes with a reported MVA phenotype (notebooks/utils/track2_step6_mva_druggability_scan.py). Only 2 of 108 high-confidence first-shell interactors have any approved drug, neither relevant to chromosome segregation, so the druggability gap is general to MVA.
 Full detail: output/track2/lostanos_track2_report.md and docs/01-procedure.md, docs/02-findings.md.</t>
         </is>
       </c>
@@ -817,7 +818,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>We start from the Track 1 result, a compound-heterozygous BUB1B genotype (stop-gain p.Leu751*, predicted null via NMD; missense p.Asn1016Lys in the pseudokinase domain, probably hypomorphic), and characterise the mechanism as partial loss of BubR1 function leading to spindle assembly checkpoint weakness, mis-segregation and mosaic aneuploidy, with a separate senescence arm. We mapped a 35-protein target panel, each annotated with its relationship to BUB1B and the desired direction of modulation, to approved drugs through ChEMBL and DGIdb, using STRING network distance as supporting evidence. The central finding is that proximity and druggability are inversely related: none of the 18 proteins at network distance 1 from BUB1B has an approved drug acting in the desired direction, and all 26 approved concordant drugs act two or more steps away or with no network path. No approved drug corrects the defect itself, so the task becomes choosing which consequence is worth addressing, honestly. Routes were scored on five weighted axes with mechanistic relevance and directionality dominant, and discarded routes are reported with an explicit reason category, including phenotype mismatch: two well-evidenced MVA mechanisms (heart, microcephaly) were set aside because this child does not present those features. Two hypotheses result. H1 (0.817): NAD+ precursors (niacin, nicotinamide riboside) supporting SIRT2-mediated stabilisation of residual BubR1 - the only route acting on BubR1 quantity, with paediatric tolerability data from ataxia-telangiectasia and a randomised trial in Werner syndrome. Its open contradiction is that rhabdomyosarcoma cells depend on BUB1B and this child has had rhabdomyosarcoma; we frame it as a remission-maintenance hypothesis gated on a paired rescue-versus-tumour-proliferation cell screen. H2 (0.667): targeting BubR1-driven cellular senescence, which in BubR1-hypomorphic mice drives the muscle wasting this child presents. Because senolysis removes a tumour-suppressive state, we propose low-dose rapalogs as senomorphics that suppress the SASP without killing cells and have paediatric rhabdomyosarcoma exposure data. Strengths: direction-aware drug mapping (which correctly rejects the most prominent network hits, PLK1 and CENPE inhibitors), categorised discards, phenotype-anchored filtering, transparent weights, fully reproducible public-data pipeline that generalises to other genes by swapping the target panel. Limitations: the N1016K effect and variant phase are unproven; mechanistic evidence is mostly from BubR1-hypomorphic mice; no senomorphic or NAD+ precursor has been tested in BubR1-deficient human cells; scores are hand-weighted; CMap/LINCS transcriptomic support was not performed. All proposals are hypotheses for experimental follow-up, not clinical recommendations.</t>
+          <t>We start from the Track 1 result, a compound-heterozygous BUB1B genotype (stop-gain p.Leu751*, predicted null via NMD; missense p.Asn1016Lys in the pseudokinase domain, probably hypomorphic), and characterise the mechanism as partial loss of BubR1 function leading to spindle assembly checkpoint weakness, mis-segregation and mosaic aneuploidy, with a separate senescence arm. We mapped a 35-protein target panel, each annotated with its relationship to BUB1B and the desired direction of modulation, to approved drugs through ChEMBL and DGIdb, using STRING network distance as supporting evidence. The central finding is that proximity and druggability are inversely related: none of the 18 proteins at network distance 1 from BUB1B has an approved drug acting in the desired direction, and all 26 approved concordant drugs act two or more steps away or with no network path. No approved drug corrects the defect itself, so the task becomes choosing which consequence is worth addressing, honestly. Routes were scored on five weighted axes with mechanistic relevance and directionality dominant, and discarded routes are reported with an explicit reason category, including phenotype mismatch: two well-evidenced MVA mechanisms (heart, microcephaly) were set aside because this child does not present those features. Two hypotheses result. H1 (0.817): NAD+ precursors (niacin, nicotinamide riboside) supporting SIRT2-mediated stabilisation of residual BubR1 - the only route acting on BubR1 quantity, with paediatric tolerability data from ataxia-telangiectasia and a randomised trial in Werner syndrome. Its open contradiction is that rhabdomyosarcoma cells depend on BUB1B and this child has had rhabdomyosarcoma; we frame it as a remission-maintenance hypothesis gated on a paired rescue-versus-tumour-proliferation cell screen. H2 (0.667): targeting BubR1-driven cellular senescence, which in BubR1-hypomorphic mice drives the muscle wasting this child presents. Because senolysis removes a tumour-suppressive state, we propose low-dose rapalogs as senomorphics that suppress the SASP without killing cells and have paediatric rhabdomyosarcoma exposure data. An automatic re-run over all eight known MVA genes shows the gap is disease-wide: 2 of 108 first-shell interactors carry any approved drug, neither relevant to the mitotic defect. The proposed experiments would also give the child's unclassified missense variant functional evidence for ACMG classification. Strengths: direction-aware drug mapping (which correctly rejects the most prominent network hits, PLK1 and CENPE inhibitors), categorised discards, phenotype-anchored filtering, transparent weights, fully reproducible public-data pipeline that generalises to other genes by swapping the target panel. Limitations: the N1016K effect and variant phase are unproven; mechanistic evidence is mostly from BubR1-hypomorphic mice; no senomorphic or NAD+ precursor has been tested in BubR1-deficient human cells; scores are hand-weighted; CMap/LINCS transcriptomic support was not performed. All proposals are hypotheses for experimental follow-up, not clinical recommendations.</t>
         </is>
       </c>
     </row>

--- a/output/track2/lostanos_track2_methods_description.xlsx
+++ b/output/track2/lostanos_track2_methods_description.xlsx
@@ -709,7 +709,7 @@
 3) Drugs: each protein was resolved to UniProt and mapped to approved drugs via ChEMBL (all targets containing the protein, salts collapsed to parent), cross-checked with DGIdb, with STRING network distance to BUB1B as supporting evidence only. Each drug-target link records whether the drug acts in the desired direction.
 4) Prioritisation: surviving routes were scored 0-3 on mechanistic relevance (weight 0.35), directionality (0.20), experimental evidence (0.20), human exposure (0.15) and tractability (0.10), so drug availability alone cannot carry a hypothesis. Routes were discarded with an explicit category (no approved drug, wrong direction, phenotype not present in this child, published negative result, toxicity rather than rescue).
 5) Follow-up: for the two prioritised hypotheses we searched for ways to mitigate their tumour-related drawbacks (remission-maintenance framing for H1; senomorphic rapalogs as an alternative to senolytics for H2).
-6) Scalability: we re-ran the drug lookup automatically for all eight genes with a reported MVA phenotype (notebooks/utils/track2_step6_mva_druggability_scan.py). Only 2 of 108 high-confidence first-shell interactors have any approved drug, neither relevant to chromosome segregation, so the druggability gap is general to MVA.
+6) Scalability: we re-ran the drug lookup automatically for all eight genes with a reported MVA or MVA-like phenotype (notebooks/utils/track2_step6_mva_druggability_scan.py). Only 2 of 108 high-confidence first-shell interactors have any approved drug, neither relevant to chromosome segregation, so the druggability gap is general to MVA.
 Full detail: output/track2/lostanos_track2_report.md and docs/01-procedure.md, docs/02-findings.md.</t>
         </is>
       </c>
@@ -722,7 +722,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TODO (team): provider, plan/tier and data-handling setting for each AI tool used (Claude and Gemini).</t>
+          <t>TODO BEFORE SUBMISSION (team, required by the organisers): provider, plan/tier and data-handling setting for each AI tool used (Claude and Gemini).</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Only publicly available drug/target databases and published literature. No proprietary data. No patient data are used in Track 2 beyond the gene and protein-level variant identity from Track 1.</t>
+          <t>Only publicly available drug/target databases and published literature. No proprietary data. No patient data beyond the Track 1 variant identity and the documented phenotype is used in Track 2.</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>TODO (team): estimate of person-hours. Computational cost is negligible: Step 3 drug mapping runs in ~5 min against public APIs; Step 4 scoring is instant and offline.</t>
+          <t>TODO BEFORE SUBMISSION (team): estimate of person-hours. Computational cost is negligible: Step 3 drug mapping runs in ~5 min against public APIs; Step 4 scoring is instant and offline; the Step 6 MVA-wide scan runs in ~4 min.</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>We start from the Track 1 result, a compound-heterozygous BUB1B genotype (stop-gain p.Leu751*, predicted null via NMD; missense p.Asn1016Lys in the pseudokinase domain, probably hypomorphic), and characterise the mechanism as partial loss of BubR1 function leading to spindle assembly checkpoint weakness, mis-segregation and mosaic aneuploidy, with a separate senescence arm. We mapped a 35-protein target panel, each annotated with its relationship to BUB1B and the desired direction of modulation, to approved drugs through ChEMBL and DGIdb, using STRING network distance as supporting evidence. The central finding is that proximity and druggability are inversely related: none of the 18 proteins at network distance 1 from BUB1B has an approved drug acting in the desired direction, and all 26 approved concordant drugs act two or more steps away or with no network path. No approved drug corrects the defect itself, so the task becomes choosing which consequence is worth addressing, honestly. Routes were scored on five weighted axes with mechanistic relevance and directionality dominant, and discarded routes are reported with an explicit reason category, including phenotype mismatch: two well-evidenced MVA mechanisms (heart, microcephaly) were set aside because this child does not present those features. Two hypotheses result. H1 (0.817): NAD+ precursors (niacin, nicotinamide riboside) supporting SIRT2-mediated stabilisation of residual BubR1 - the only route acting on BubR1 quantity, with paediatric tolerability data from ataxia-telangiectasia and a randomised trial in Werner syndrome. Its open contradiction is that rhabdomyosarcoma cells depend on BUB1B and this child has had rhabdomyosarcoma; we frame it as a remission-maintenance hypothesis gated on a paired rescue-versus-tumour-proliferation cell screen. H2 (0.667): targeting BubR1-driven cellular senescence, which in BubR1-hypomorphic mice drives the muscle wasting this child presents. Because senolysis removes a tumour-suppressive state, we propose low-dose rapalogs as senomorphics that suppress the SASP without killing cells and have paediatric rhabdomyosarcoma exposure data. An automatic re-run over all eight known MVA genes shows the gap is disease-wide: 2 of 108 first-shell interactors carry any approved drug, neither relevant to the mitotic defect. The proposed experiments would also give the child's unclassified missense variant functional evidence for ACMG classification. Strengths: direction-aware drug mapping (which correctly rejects the most prominent network hits, PLK1 and CENPE inhibitors), categorised discards, phenotype-anchored filtering, transparent weights, fully reproducible public-data pipeline that generalises to other genes by swapping the target panel. Limitations: the N1016K effect and variant phase are unproven; mechanistic evidence is mostly from BubR1-hypomorphic mice; no senomorphic or NAD+ precursor has been tested in BubR1-deficient human cells; scores are hand-weighted; CMap/LINCS transcriptomic support was not performed. All proposals are hypotheses for experimental follow-up, not clinical recommendations.</t>
+          <t>We start from the Track 1 result, a compound-heterozygous BUB1B genotype (stop-gain p.Leu751*, predicted null via NMD; missense p.Asn1016Lys in the pseudokinase domain, probably hypomorphic), and characterise the mechanism as partial loss of BubR1 function leading to spindle assembly checkpoint weakness, mis-segregation and mosaic aneuploidy, with a separate senescence arm. We mapped a 35-protein target panel, each annotated with its relationship to BUB1B and the desired direction of modulation, to approved drugs through ChEMBL and DGIdb, using STRING network distance as supporting evidence. The central finding is that proximity and druggability are inversely related: none of the 18 proteins at network distance 1 from BUB1B has an approved drug acting in the desired direction, and all 26 approved concordant drugs act two or more steps away or with no network path. No approved drug corrects the defect itself, so the task becomes choosing which consequence is worth addressing, honestly. Routes were scored on five weighted axes with mechanistic relevance and directionality dominant, and discarded routes are reported with an explicit reason category, including phenotype mismatch: two well-evidenced MVA mechanisms (heart, microcephaly) were set aside because this child does not present those features. Two hypotheses result. H1 (0.817): NAD+ precursors (niacin, nicotinamide riboside) supporting SIRT2-mediated stabilisation of residual BubR1 - the only route acting on BubR1 quantity, with paediatric tolerability data from ataxia-telangiectasia and a randomised trial in Werner syndrome. Its open contradiction is that rhabdomyosarcoma cells depend on BUB1B and this child has had rhabdomyosarcoma; we frame it as a remission-maintenance hypothesis gated on a paired rescue-versus-tumour-proliferation cell screen. H2 (0.667): targeting BubR1-driven cellular senescence, which in BubR1-hypomorphic mice drives the muscle wasting this child presents. Because senolysis removes a tumour-suppressive state, we propose low-dose rapalogs as senomorphics that suppress the SASP without killing cells; one of them (temsirolimus) has paediatric rhabdomyosarcoma exposure data from a phase 3 trial. An automatic re-run over all eight known MVA genes shows the gap is disease-wide: 2 of 108 first-shell interactors carry any approved drug, neither relevant to the mitotic defect. The proposed experiments would also give the child's unclassified missense variant functional evidence for ACMG classification. Strengths: direction-aware drug mapping (which correctly rejects the most prominent network hits, PLK1 and CENPE inhibitors), categorised discards, phenotype-anchored filtering, transparent weights, fully reproducible public-data pipeline that generalises to other genes by swapping the target panel. Limitations: the N1016K effect and variant phase are unproven; mechanistic evidence is mostly from BubR1-hypomorphic mice; no senomorphic or NAD+ precursor has been tested in BubR1-deficient human cells; scores are hand-weighted; CMap/LINCS transcriptomic support was not performed. All proposals are hypotheses for experimental follow-up, not clinical recommendations.</t>
         </is>
       </c>
     </row>

--- a/output/track2/lostanos_track2_methods_description.xlsx
+++ b/output/track2/lostanos_track2_methods_description.xlsx
@@ -722,7 +722,8 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TODO BEFORE SUBMISSION (team, required by the organisers): provider, plan/tier and data-handling setting for each AI tool used (Claude and Gemini).</t>
+          <t>Google Cloud Vertex AI (Gemini API), training on our data disabled by Google's data-use policy, no 👍/👎 feedback provided.
+Anthropic, Claude Team plan (Claude Code desktop app, Claude Opus), commercial terms, no training on customer content, no 👍/👎 feedback provided.</t>
         </is>
       </c>
     </row>

--- a/output/track2/lostanos_track2_methods_description.xlsx
+++ b/output/track2/lostanos_track2_methods_description.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>TODO BEFORE SUBMISSION (team): estimate of person-hours. Computational cost is negligible: Step 3 drug mapping runs in ~5 min against public APIs; Step 4 scoring is instant and offline; the Step 6 MVA-wide scan runs in ~4 min.</t>
+          <t>About 20 person-hours of team effort for Track 2. Computational cost is negligible: Step 3 drug mapping runs in ~5 min against public APIs; Step 4 scoring is instant and offline; the Step 6 MVA-wide scan runs in ~4 min.</t>
         </is>
       </c>
     </row>
